--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_114_R12.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_114_R12.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.531700000000001</v>
+        <v>9.648999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7079</v>
+        <v>7.5899</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8238</v>
+        <v>2.059</v>
       </c>
       <c r="G2" t="n">
         <v>7.8391</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.5122</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0351</v>
+        <v>-0.1531</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5944</v>
+        <v>-0.3591</v>
       </c>
       <c r="V2" t="n">
         <v>0.9304</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9496</v>
+        <v>4.5615</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1579</v>
+        <v>2.5681</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7917</v>
+        <v>1.9934</v>
       </c>
       <c r="G3" t="n">
         <v>2.7865</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7714</v>
+        <v>0.3833</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9752</v>
+        <v>0.3855</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2038</v>
+        <v>-0.0022</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.983</v>
+        <v>3.4713</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3684</v>
+        <v>3.7223</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3855</v>
+        <v>-0.251</v>
       </c>
       <c r="G4" t="n">
         <v>3.7469</v>
@@ -766,13 +766,13 @@
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0835</v>
+        <v>0.4048</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1098</v>
+        <v>0.244</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0264</v>
+        <v>0.1608</v>
       </c>
       <c r="V4" t="n">
         <v>-1.6083</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3409</v>
+        <v>1.9799</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1637</v>
+        <v>2.0504</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8228</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2672</v>
+        <v>2.5136</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4804</v>
+        <v>-0.1297</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7869</v>
+        <v>2.6433</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6649</v>
+        <v>3.5364</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8184</v>
+        <v>0.6288</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8465</v>
+        <v>2.9076</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3977</v>
+        <v>-1.0227</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3381</v>
+        <v>-0.7584</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9403</v>
+        <v>-0.2643</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1639</v>
+        <v>0.1621</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6765</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5127</v>
+        <v>0.2563</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8613</v>
+        <v>1.7848</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6966</v>
+        <v>2.574</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1647</v>
+        <v>-0.7892</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5136</v>
+        <v>2.2672</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1297</v>
+        <v>0.4804</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6433</v>
+        <v>1.7869</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5364</v>
+        <v>2.6649</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6288</v>
+        <v>1.8184</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9076</v>
+        <v>0.8465</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0227</v>
+        <v>-0.3977</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7584</v>
+        <v>-1.3381</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2643</v>
+        <v>0.9403</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0435</v>
+        <v>-0.3923</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4481</v>
+        <v>0.0868</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4916</v>
+        <v>-0.479</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2222</v>
+        <v>1.2051</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0391</v>
+        <v>-0.0788</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1831</v>
+        <v>1.2839</v>
       </c>
       <c r="G7" t="n">
         <v>0.7423999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8536</v>
+        <v>0.8364</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4129</v>
+        <v>0.295</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4406</v>
+        <v>0.5414</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1418</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.887</v>
+        <v>0.8899</v>
       </c>
       <c r="E8" t="n">
-        <v>0.589</v>
+        <v>1.8866</v>
       </c>
       <c r="F8" t="n">
-        <v>0.298</v>
+        <v>-0.9967</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7129</v>
+        <v>3.7609</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3181</v>
+        <v>2.1716</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3948</v>
+        <v>1.5893</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4128</v>
+        <v>3.3471</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6973</v>
+        <v>3.277</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2845</v>
+        <v>0.0701</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3001</v>
+        <v>0.4139</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3792</v>
+        <v>-1.1053</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6793</v>
+        <v>1.5192</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R8" t="n">
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>1.9448</v>
+        <v>-0.3196</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1246</v>
+        <v>-0.1256</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8202</v>
+        <v>-0.1939</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.5387</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7886</v>
+        <v>2.1444</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7501</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7495000000000001</v>
+        <v>0.8002</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2935</v>
+        <v>1.4114</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.544</v>
+        <v>-0.6112</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3447</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.21</v>
+        <v>-0.1592</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0141</v>
+        <v>-0.0532</v>
       </c>
       <c r="V9" t="n">
         <v>1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>M. GRIGONIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4517</v>
+        <v>-0.0155</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4148</v>
+        <v>-0.2072</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9631</v>
+        <v>0.1917</v>
       </c>
       <c r="G10" t="n">
-        <v>3.7609</v>
+        <v>0.1417</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1716</v>
+        <v>-0.0155</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5893</v>
+        <v>0.1573</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3471</v>
+        <v>0.0168</v>
       </c>
       <c r="K10" t="n">
-        <v>3.277</v>
+        <v>0.0168</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0701</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4139</v>
+        <v>0.1249</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1053</v>
+        <v>-0.0323</v>
       </c>
       <c r="O10" t="n">
-        <v>1.5192</v>
+        <v>0.1573</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7578</v>
+        <v>-0.1573</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5975</v>
+        <v>-0.224</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1603</v>
+        <v>0.0668</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. GRIGONIS</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.15</v>
+        <v>-0.2411</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2072</v>
+        <v>-0.2367</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0573</v>
+        <v>-0.0045</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1417</v>
+        <v>1.7129</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0155</v>
+        <v>1.3181</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1573</v>
+        <v>0.3948</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0168</v>
+        <v>1.4128</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0168</v>
+        <v>1.6973</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.2845</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1249</v>
+        <v>0.3001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0323</v>
+        <v>-0.3792</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1573</v>
+        <v>0.6793</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2917</v>
+        <v>0.8167</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.224</v>
+        <v>0.2989</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0677</v>
+        <v>0.5177</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-2.5387</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5125</v>
+        <v>-0.3273</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9357</v>
+        <v>-0.8178</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4232</v>
+        <v>0.4905</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4826</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0299</v>
+        <v>0.1553</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1195</v>
+        <v>0.1867</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7995</v>
+        <v>-1.2427</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.741</v>
+        <v>-1.9153</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9414</v>
+        <v>0.6726</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5778</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3866</v>
+        <v>0.9434</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6721</v>
+        <v>0.1535</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0587</v>
+        <v>0.7899</v>
       </c>
       <c r="V13" t="n">
         <v>-1.6083</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>22.5149</v>
+        <v>22.5151</v>
       </c>
       <c r="E14" t="n">
-        <v>18.547</v>
+        <v>18.5469</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9678</v>
+        <v>3.968</v>
       </c>
       <c r="G14" t="n">
         <v>24.1061</v>
       </c>
       <c r="H14" t="n">
-        <v>8.865499999999999</v>
+        <v>8.865500000000001</v>
       </c>
       <c r="I14" t="n">
         <v>15.2409</v>
@@ -1528,7 +1528,7 @@
         <v>7.661200000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.05869999999999997</v>
+        <v>-0.05870000000000003</v>
       </c>
       <c r="N14" t="n">
         <v>-7.6382</v>
@@ -1537,7 +1537,7 @@
         <v>7.579400000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.0002000000000004221</v>
+        <v>-0.0001999999999997837</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.5976</v>
@@ -1549,7 +1549,7 @@
         <v>2.1614</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7291999999999997</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="U14" t="n">
         <v>1.4322</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0453</v>
+        <v>-0.6876</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7468</v>
+        <v>-1.2038</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.7015</v>
+        <v>0.5162</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.6919</v>
+        <v>-0.952</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3634</v>
+        <v>-0.5305</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.0553</v>
+        <v>-0.4216</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5798</v>
+        <v>-0.4334</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7916</v>
+        <v>0.3529</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.2118</v>
+        <v>-0.7863</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.2717</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.4282</v>
+        <v>-0.8834</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8435</v>
+        <v>0.3648</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2707</v>
+        <v>-0.6633</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4144</v>
+        <v>-0.7703</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1436</v>
+        <v>0.107</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>B. ELLIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6112</v>
+        <v>-0.7271</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3386</v>
+        <v>1.5919</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.9498</v>
+        <v>-2.3191</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.7493</v>
+        <v>-3.6981</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.3733</v>
+        <v>-3.1394</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.376</v>
+        <v>-0.5587</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8772</v>
+        <v>-1.5069</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5482</v>
+        <v>-1.8983</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.4255</v>
+        <v>0.3914</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.8721</v>
+        <v>-2.1912</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.9215</v>
+        <v>-1.241</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9505</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7644</v>
+        <v>-0.3332</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3936</v>
+        <v>-0.1177</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3708</v>
+        <v>-0.2155</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2862</v>
+        <v>2.1444</v>
       </c>
       <c r="W16" t="n">
-        <v>2.8223</v>
+        <v>3.2166</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7047</v>
+        <v>-0.7836</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3217</v>
+        <v>3.011</v>
       </c>
       <c r="F17" t="n">
-        <v>0.617</v>
+        <v>-3.7946</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.952</v>
+        <v>-1.2988</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5305</v>
+        <v>-0.7334000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4216</v>
+        <v>-0.5654</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4334</v>
+        <v>2.8691</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3529</v>
+        <v>1.852</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7863</v>
+        <v>1.0171</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-4.1679</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8834</v>
+        <v>-2.5854</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3648</v>
+        <v>-1.5825</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6805</v>
+        <v>-0.0362</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8883</v>
+        <v>0.1419</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2078</v>
+        <v>-0.1781</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8265</v>
+        <v>-0.8094</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1751</v>
+        <v>-1.0571</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3485</v>
+        <v>0.2477</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2077</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0075</v>
+        <v>0.0246</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3062</v>
+        <v>0.2054</v>
       </c>
       <c r="V18" t="n">
         <v>0.1418</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. ELLIS</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9637</v>
+        <v>-1.202</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1201</v>
+        <v>1.3314</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0838</v>
+        <v>-2.5335</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.6981</v>
+        <v>-2.6919</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.1394</v>
+        <v>1.3634</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5587</v>
+        <v>-4.0553</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5069</v>
+        <v>1.5798</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.8983</v>
+        <v>3.7916</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3914</v>
+        <v>-2.2118</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1912</v>
+        <v>-4.2717</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.241</v>
+        <v>-2.4282</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-1.8435</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1598</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5698</v>
+        <v>1.0233</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5895</v>
+        <v>0.999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0198</v>
+        <v>0.0244</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1444</v>
+        <v>0.9304</v>
       </c>
       <c r="W19" t="n">
-        <v>3.2166</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2547</v>
+        <v>-1.2339</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7751</v>
+        <v>1.9848</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.0298</v>
+        <v>-3.2187</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2988</v>
+        <v>-5.7493</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-2.3733</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5654</v>
+        <v>-3.376</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8691</v>
+        <v>-0.8772</v>
       </c>
       <c r="K20" t="n">
-        <v>1.852</v>
+        <v>0.5482</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0171</v>
+        <v>-1.4255</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.1679</v>
+        <v>-4.8721</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.5854</v>
+        <v>-2.9215</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5825</v>
+        <v>-1.9505</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5074</v>
+        <v>0.1417</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.094</v>
+        <v>0.0397</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4134</v>
+        <v>0.1019</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>2.2862</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.8223</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="21">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1394</v>
+        <v>-2.8699</v>
       </c>
       <c r="E23" t="n">
-        <v>2.3531</v>
+        <v>2.589</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.4925</v>
+        <v>-5.4589</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1855</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4178</v>
+        <v>-0.1483</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2434</v>
+        <v>-0.0075</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1744</v>
+        <v>-0.1408</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3138</v>
+        <v>-2.9942</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7114</v>
+        <v>-2.5934</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6025</v>
+        <v>-0.4008</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8225</v>
@@ -2326,13 +2326,13 @@
         <v>0.232</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7776</v>
+        <v>-0.458</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4402</v>
+        <v>-0.3222</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3374</v>
+        <v>-0.1357</v>
       </c>
       <c r="V24" t="n">
         <v>1.214</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.83</v>
+        <v>-3.4089</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1408</v>
+        <v>-1.7869</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6892</v>
+        <v>-1.622</v>
       </c>
       <c r="G25" t="n">
         <v>-1.174</v>
@@ -2404,13 +2404,13 @@
         <v>0.232</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5685</v>
+        <v>-0.1474</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2987</v>
+        <v>0.0551</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2697</v>
+        <v>-0.2025</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.5056</v>
+        <v>-4.3876</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.8693</v>
+        <v>-3.7513</v>
       </c>
       <c r="F26" t="n">
         <v>-0.6363</v>
@@ -2482,10 +2482,10 @@
         <v>0.232</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6133</v>
+        <v>-0.4953</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5149</v>
+        <v>-0.3969</v>
       </c>
       <c r="U26" t="n">
         <v>-0.0984</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-22.5149</v>
+        <v>-22.5148</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.4321</v>
+        <v>-3.4319</v>
       </c>
       <c r="F27" t="n">
-        <v>-19.083</v>
+        <v>-19.0831</v>
       </c>
       <c r="G27" t="n">
         <v>-24.1062</v>
@@ -2536,10 +2536,10 @@
         <v>0.05889999999999973</v>
       </c>
       <c r="K27" t="n">
-        <v>7.6383</v>
+        <v>7.638299999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>-7.5794</v>
+        <v>-7.579400000000001</v>
       </c>
       <c r="M27" t="n">
         <v>-24.1649</v>
@@ -2560,13 +2560,13 @@
         <v>11.5979</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.1616</v>
+        <v>-2.1614</v>
       </c>
       <c r="T27" t="n">
         <v>-1.4322</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.7291</v>
+        <v>-0.7291000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>3.7527</v>
